--- a/cypress/downloads/Client_Employer_Report.xlsx
+++ b/cypress/downloads/Client_Employer_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -106,6 +106,15 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
@@ -115,9 +124,6 @@
     <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
@@ -128,6 +134,9 @@
   </x:si>
   <x:si>
     <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
@@ -194,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L11" totalsRowShown="0">
-  <x:autoFilter ref="A1:L11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L12" totalsRowShown="0">
+  <x:autoFilter ref="A1:L12"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -502,7 +511,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L11"/>
+  <x:dimension ref="A1:L12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:12">
@@ -637,63 +646,75 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s">
+      <x:c r="J6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>16</x:v>
@@ -704,13 +725,27 @@
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:12">
+      <x:c r="A12" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Client_Employer_Report.xlsx
+++ b/cypress/downloads/Client_Employer_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -55,91 +55,145 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>main husbandmain husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main husband</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>supplier emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>outnz source</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AgricultureFarming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>recruiter emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+64211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">employer nabem </x:t>
   </x:si>
   <x:si>
     <x:t>outcource nz</x:t>
   </x:si>
   <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>recruiter emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+64211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TST </x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -203,8 +257,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L12" totalsRowShown="0">
-  <x:autoFilter ref="A1:L12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L17" totalsRowShown="0">
+  <x:autoFilter ref="A1:L17"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -511,7 +565,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L12"/>
+  <x:dimension ref="A1:L17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:12">
@@ -556,196 +610,305 @@
       <x:c r="A2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
+      <x:c r="I2" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12">
       <x:c r="A3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:12">
+      <x:c r="A13" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:12">
+      <x:c r="A14" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:12">
+      <x:c r="A15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:12">
+      <x:c r="A16" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:12">
+      <x:c r="A17" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Client_Employer_Report.xlsx
+++ b/cypress/downloads/Client_Employer_Report.xlsx
@@ -94,6 +94,54 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">employer nabem </x:t>
+  </x:si>
+  <x:si>
+    <x:t>outcource nz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
     <x:t>recruiter emp</x:t>
   </x:si>
   <x:si>
@@ -106,94 +154,46 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">testt </x:t>
   </x:si>
   <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>test nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">employer nabem </x:t>
-  </x:si>
-  <x:si>
-    <x:t>outcource nz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
     <x:t>15</x:t>
   </x:si>
   <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teacher</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">TST </x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teacher</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -659,204 +659,192 @@
       <x:c r="C4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="I5" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="L5" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
+      <x:c r="J14" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
@@ -865,10 +853,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>54</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
@@ -876,39 +876,39 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Client_Employer_Report.xlsx
+++ b/cypress/downloads/Client_Employer_Report.xlsx
@@ -94,6 +94,33 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>recruiter emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>+64211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
     <x:t>mlian</x:t>
   </x:si>
   <x:si>
@@ -103,103 +130,76 @@
     <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
     <x:t>6</x:t>
   </x:si>
   <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">employer nabem </x:t>
+  </x:si>
+  <x:si>
+    <x:t>outcource nz</x:t>
+  </x:si>
+  <x:si>
     <x:t>basic web</x:t>
   </x:si>
   <x:si>
     <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">testhshhd...1 </x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">employer nabem </x:t>
-  </x:si>
-  <x:si>
-    <x:t>outcource nz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>recruiter emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+64211267313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testt </x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test nabeel</x:t>
-  </x:si>
-  <x:si>
     <x:t>16</x:t>
   </x:si>
   <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
     <x:t>nbaaa Efgh</x:t>
   </x:si>
   <x:si>
     <x:t>Teacher</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -665,219 +665,231 @@
       <x:c r="C4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L13" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L14" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
@@ -885,22 +897,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:12">
@@ -908,39 +908,39 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
+      <x:c r="J18" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
         <x:v>61</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/Client_Employer_Report.xlsx
+++ b/cypress/downloads/Client_Employer_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -94,6 +94,60 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>mlian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testhshhd...1 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TST again</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">employer nabem </x:t>
+  </x:si>
+  <x:si>
+    <x:t>outcource nz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
     <x:t>recruiter emp</x:t>
   </x:si>
   <x:si>
@@ -106,94 +160,61 @@
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>nab ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel,team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">testt </x:t>
   </x:si>
   <x:si>
-    <x:t>Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>test nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mlian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nab ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nabeel Ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">employer nabem </x:t>
-  </x:si>
-  <x:si>
-    <x:t>outcource nz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">testhshhd...1 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TST again</x:t>
-  </x:si>
-  <x:si>
     <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mamam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>te</x:t>
+  </x:si>
+  <x:si>
+    <x:t>r</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tt@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expire thing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>nbaaa Efgh</x:t>
@@ -263,8 +284,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L18" totalsRowShown="0">
-  <x:autoFilter ref="A1:L18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:L19" totalsRowShown="0">
+  <x:autoFilter ref="A1:L19"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="EZM ID"/>
@@ -571,7 +592,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L18"/>
+  <x:dimension ref="A1:L19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:12">
@@ -665,217 +686,181 @@
       <x:c r="C4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="I5" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="L5" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="J13" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
+      <x:c r="L13" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:12">
@@ -883,13 +868,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
@@ -897,10 +894,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>56</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:12">
@@ -908,10 +917,22 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>58</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:12">
@@ -919,27 +940,53 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:12">
+      <x:c r="A19" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D18" s="0" t="s">
+      <x:c r="D19" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E18" s="0" t="s">
+      <x:c r="E19" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="H18" s="0" t="s">
+      <x:c r="H19" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
+      <x:c r="I19" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
+      <x:c r="K19" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
